--- a/wellanders/kommer_att_corrected.xlsx
+++ b/wellanders/kommer_att_corrected.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\DGU\Repos\Cassandra\wellanders\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28065A22-99DD-472E-A95C-2DC236291E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A42DB4A-32F7-4C63-9972-A04F39DE7A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -825,8 +825,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
@@ -1207,7 +1206,6 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="20" width="18.7109375" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1271,7 +1269,7 @@
       <c r="T1" t="s">
         <v>101</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1340,7 +1338,7 @@
         <f>SUM(B2:T2)</f>
         <v>0</v>
       </c>
-      <c r="V2" s="1">
+      <c r="V2">
         <v>0</v>
       </c>
     </row>
@@ -1405,11 +1403,11 @@
       <c r="T3">
         <v>0</v>
       </c>
-      <c r="U3" s="1">
+      <c r="U3">
         <f t="shared" ref="U3:U66" si="0">SUM(B3:T3)</f>
         <v>0</v>
       </c>
-      <c r="V3" s="1">
+      <c r="V3">
         <v>0</v>
       </c>
     </row>
@@ -1474,11 +1472,11 @@
       <c r="T4">
         <v>0</v>
       </c>
-      <c r="U4" s="1">
+      <c r="U4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V4" s="1">
+      <c r="V4">
         <v>0</v>
       </c>
     </row>
@@ -1543,11 +1541,11 @@
       <c r="T5">
         <v>0</v>
       </c>
-      <c r="U5" s="1">
+      <c r="U5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V5" s="1">
+      <c r="V5">
         <v>0</v>
       </c>
     </row>
@@ -1612,11 +1610,11 @@
       <c r="T6">
         <v>0</v>
       </c>
-      <c r="U6" s="1">
+      <c r="U6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V6" s="1">
+      <c r="V6">
         <v>0</v>
       </c>
     </row>
@@ -1681,11 +1679,11 @@
       <c r="T7">
         <v>0</v>
       </c>
-      <c r="U7" s="1">
+      <c r="U7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V7" s="1">
+      <c r="V7">
         <v>0</v>
       </c>
     </row>
@@ -1750,11 +1748,11 @@
       <c r="T8">
         <v>0</v>
       </c>
-      <c r="U8" s="1">
+      <c r="U8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V8" s="1">
+      <c r="V8">
         <v>0</v>
       </c>
     </row>
@@ -1819,11 +1817,11 @@
       <c r="T9">
         <v>0</v>
       </c>
-      <c r="U9" s="1">
+      <c r="U9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V9" s="1">
+      <c r="V9">
         <v>0</v>
       </c>
     </row>
@@ -1888,11 +1886,11 @@
       <c r="T10">
         <v>0</v>
       </c>
-      <c r="U10" s="1">
+      <c r="U10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V10" s="1">
+      <c r="V10">
         <v>0</v>
       </c>
     </row>
@@ -1957,11 +1955,11 @@
       <c r="T11">
         <v>0</v>
       </c>
-      <c r="U11" s="1">
+      <c r="U11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V11" s="1">
+      <c r="V11">
         <v>0</v>
       </c>
     </row>
@@ -2026,11 +2024,11 @@
       <c r="T12">
         <v>0</v>
       </c>
-      <c r="U12" s="1">
+      <c r="U12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V12" s="1">
+      <c r="V12">
         <v>0</v>
       </c>
     </row>
@@ -2095,11 +2093,11 @@
       <c r="T13">
         <v>0</v>
       </c>
-      <c r="U13" s="1">
+      <c r="U13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V13" s="1">
+      <c r="V13">
         <v>0</v>
       </c>
     </row>
@@ -2164,11 +2162,11 @@
       <c r="T14">
         <v>0</v>
       </c>
-      <c r="U14" s="1">
+      <c r="U14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V14" s="1">
+      <c r="V14">
         <v>0</v>
       </c>
     </row>
@@ -2233,11 +2231,11 @@
       <c r="T15">
         <v>0</v>
       </c>
-      <c r="U15" s="1">
+      <c r="U15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V15" s="1">
+      <c r="V15">
         <v>0</v>
       </c>
     </row>
@@ -2302,11 +2300,11 @@
       <c r="T16">
         <v>0</v>
       </c>
-      <c r="U16" s="1">
+      <c r="U16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V16" s="1">
+      <c r="V16">
         <v>0</v>
       </c>
     </row>
@@ -2371,11 +2369,11 @@
       <c r="T17">
         <v>0</v>
       </c>
-      <c r="U17" s="1">
+      <c r="U17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V17" s="1">
+      <c r="V17">
         <v>0</v>
       </c>
     </row>
@@ -2440,11 +2438,11 @@
       <c r="T18">
         <v>0</v>
       </c>
-      <c r="U18" s="1">
+      <c r="U18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V18" s="1">
+      <c r="V18">
         <v>0</v>
       </c>
     </row>
@@ -2509,11 +2507,11 @@
       <c r="T19">
         <v>0</v>
       </c>
-      <c r="U19" s="1">
+      <c r="U19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V19" s="1">
+      <c r="V19">
         <v>0</v>
       </c>
     </row>
@@ -2578,11 +2576,11 @@
       <c r="T20">
         <v>0</v>
       </c>
-      <c r="U20" s="1">
+      <c r="U20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V20" s="1">
+      <c r="V20">
         <v>0</v>
       </c>
     </row>
@@ -2647,11 +2645,11 @@
       <c r="T21">
         <v>0</v>
       </c>
-      <c r="U21" s="1">
+      <c r="U21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V21" s="1">
+      <c r="V21">
         <v>0</v>
       </c>
     </row>
@@ -2716,11 +2714,11 @@
       <c r="T22">
         <v>0</v>
       </c>
-      <c r="U22" s="1">
+      <c r="U22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V22" s="1">
+      <c r="V22">
         <v>0</v>
       </c>
     </row>
@@ -2785,11 +2783,11 @@
       <c r="T23">
         <v>0</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V23" s="1">
+      <c r="V23">
         <v>0</v>
       </c>
     </row>
@@ -2854,11 +2852,11 @@
       <c r="T24">
         <v>0</v>
       </c>
-      <c r="U24" s="1">
+      <c r="U24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V24" s="1">
+      <c r="V24">
         <v>0</v>
       </c>
     </row>
@@ -2923,11 +2921,11 @@
       <c r="T25">
         <v>0</v>
       </c>
-      <c r="U25" s="1">
+      <c r="U25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V25" s="1">
+      <c r="V25">
         <v>0</v>
       </c>
     </row>
@@ -2992,11 +2990,11 @@
       <c r="T26">
         <v>0</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V26" s="1">
+      <c r="V26">
         <v>0</v>
       </c>
     </row>
@@ -3061,11 +3059,11 @@
       <c r="T27">
         <v>0</v>
       </c>
-      <c r="U27" s="1">
+      <c r="U27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V27" s="1">
+      <c r="V27">
         <v>0</v>
       </c>
     </row>
@@ -3130,11 +3128,11 @@
       <c r="T28">
         <v>0</v>
       </c>
-      <c r="U28" s="1">
+      <c r="U28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V28" s="1">
+      <c r="V28">
         <v>0</v>
       </c>
     </row>
@@ -3199,11 +3197,11 @@
       <c r="T29">
         <v>0</v>
       </c>
-      <c r="U29" s="1">
+      <c r="U29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V29" s="1">
+      <c r="V29">
         <v>0</v>
       </c>
     </row>
@@ -3268,11 +3266,11 @@
       <c r="T30">
         <v>0</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V30" s="1">
+      <c r="V30">
         <v>0</v>
       </c>
     </row>
@@ -3337,11 +3335,11 @@
       <c r="T31">
         <v>0</v>
       </c>
-      <c r="U31" s="1">
+      <c r="U31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V31" s="1">
+      <c r="V31">
         <v>0</v>
       </c>
     </row>
@@ -3406,11 +3404,11 @@
       <c r="T32">
         <v>0</v>
       </c>
-      <c r="U32" s="1">
+      <c r="U32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V32" s="1">
+      <c r="V32">
         <v>0</v>
       </c>
     </row>
@@ -3475,11 +3473,11 @@
       <c r="T33">
         <v>0</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V33" s="1">
+      <c r="V33">
         <v>0</v>
       </c>
     </row>
@@ -3544,11 +3542,11 @@
       <c r="T34">
         <v>0</v>
       </c>
-      <c r="U34" s="1">
+      <c r="U34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V34" s="1">
+      <c r="V34">
         <v>0</v>
       </c>
     </row>
@@ -3613,11 +3611,11 @@
       <c r="T35">
         <v>0</v>
       </c>
-      <c r="U35" s="1">
+      <c r="U35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V35" s="1">
+      <c r="V35">
         <v>0</v>
       </c>
     </row>
@@ -3682,11 +3680,11 @@
       <c r="T36">
         <v>0</v>
       </c>
-      <c r="U36" s="1">
+      <c r="U36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V36" s="1">
+      <c r="V36">
         <v>0</v>
       </c>
     </row>
@@ -3751,11 +3749,11 @@
       <c r="T37">
         <v>0</v>
       </c>
-      <c r="U37" s="1">
+      <c r="U37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V37" s="1">
+      <c r="V37">
         <v>0</v>
       </c>
     </row>
@@ -3820,11 +3818,11 @@
       <c r="T38">
         <v>33</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38">
         <f t="shared" si="0"/>
         <v>528</v>
       </c>
-      <c r="V38" s="1">
+      <c r="V38">
         <v>448</v>
       </c>
     </row>
@@ -3889,11 +3887,11 @@
       <c r="T39">
         <v>168</v>
       </c>
-      <c r="U39" s="1">
+      <c r="U39">
         <f t="shared" si="0"/>
         <v>2519</v>
       </c>
-      <c r="V39" s="1">
+      <c r="V39">
         <v>2310</v>
       </c>
     </row>
@@ -3958,11 +3956,11 @@
       <c r="T40">
         <v>214</v>
       </c>
-      <c r="U40" s="1">
+      <c r="U40">
         <f t="shared" si="0"/>
         <v>2570</v>
       </c>
-      <c r="V40" s="1">
+      <c r="V40">
         <v>2341</v>
       </c>
     </row>
@@ -4027,11 +4025,11 @@
       <c r="T41">
         <v>206</v>
       </c>
-      <c r="U41" s="1">
+      <c r="U41">
         <f t="shared" si="0"/>
         <v>2546</v>
       </c>
-      <c r="V41" s="1">
+      <c r="V41">
         <v>2335</v>
       </c>
     </row>
@@ -4096,11 +4094,11 @@
       <c r="T42">
         <v>275</v>
       </c>
-      <c r="U42" s="1">
+      <c r="U42">
         <f t="shared" si="0"/>
         <v>3464</v>
       </c>
-      <c r="V42" s="1">
+      <c r="V42">
         <v>3122</v>
       </c>
     </row>
@@ -4165,11 +4163,11 @@
       <c r="T43">
         <v>272</v>
       </c>
-      <c r="U43" s="1">
+      <c r="U43">
         <f t="shared" si="0"/>
         <v>3601</v>
       </c>
-      <c r="V43" s="1">
+      <c r="V43">
         <v>3218</v>
       </c>
     </row>
@@ -4234,11 +4232,11 @@
       <c r="T44">
         <v>304</v>
       </c>
-      <c r="U44" s="1">
+      <c r="U44">
         <f t="shared" si="0"/>
         <v>3434</v>
       </c>
-      <c r="V44" s="1">
+      <c r="V44">
         <v>3142</v>
       </c>
     </row>
@@ -4303,11 +4301,11 @@
       <c r="T45">
         <v>299</v>
       </c>
-      <c r="U45" s="1">
+      <c r="U45">
         <f t="shared" si="0"/>
         <v>3685</v>
       </c>
-      <c r="V45" s="1">
+      <c r="V45">
         <v>3315</v>
       </c>
     </row>
@@ -4372,11 +4370,11 @@
       <c r="T46">
         <v>428</v>
       </c>
-      <c r="U46" s="1">
+      <c r="U46">
         <f t="shared" si="0"/>
         <v>4858</v>
       </c>
-      <c r="V46" s="1">
+      <c r="V46">
         <v>4338</v>
       </c>
     </row>
@@ -4441,11 +4439,11 @@
       <c r="T47">
         <v>551</v>
       </c>
-      <c r="U47" s="1">
+      <c r="U47">
         <f t="shared" si="0"/>
         <v>6561</v>
       </c>
-      <c r="V47" s="1">
+      <c r="V47">
         <v>5802</v>
       </c>
     </row>
@@ -4510,11 +4508,11 @@
       <c r="T48">
         <v>604</v>
       </c>
-      <c r="U48" s="1">
+      <c r="U48">
         <f t="shared" si="0"/>
         <v>6819</v>
       </c>
-      <c r="V48" s="1">
+      <c r="V48">
         <v>6022</v>
       </c>
     </row>
@@ -4579,11 +4577,11 @@
       <c r="T49">
         <v>703</v>
       </c>
-      <c r="U49" s="1">
+      <c r="U49">
         <f t="shared" si="0"/>
         <v>8155</v>
       </c>
-      <c r="V49" s="1">
+      <c r="V49">
         <v>7218</v>
       </c>
     </row>
@@ -4648,11 +4646,11 @@
       <c r="T50">
         <v>763</v>
       </c>
-      <c r="U50" s="1">
+      <c r="U50">
         <f t="shared" si="0"/>
         <v>8947</v>
       </c>
-      <c r="V50" s="1">
+      <c r="V50">
         <v>7974</v>
       </c>
     </row>
@@ -4717,11 +4715,11 @@
       <c r="T51">
         <v>1272</v>
       </c>
-      <c r="U51" s="1">
+      <c r="U51">
         <f t="shared" si="0"/>
         <v>14023</v>
       </c>
-      <c r="V51" s="1">
+      <c r="V51">
         <v>12352</v>
       </c>
     </row>
@@ -4786,11 +4784,11 @@
       <c r="T52">
         <v>2313</v>
       </c>
-      <c r="U52" s="1">
+      <c r="U52">
         <f t="shared" si="0"/>
         <v>23561</v>
       </c>
-      <c r="V52" s="1">
+      <c r="V52">
         <v>20844</v>
       </c>
     </row>
@@ -4855,11 +4853,11 @@
       <c r="T53">
         <v>2292</v>
       </c>
-      <c r="U53" s="1">
+      <c r="U53">
         <f t="shared" si="0"/>
         <v>23379</v>
       </c>
-      <c r="V53" s="1">
+      <c r="V53">
         <v>20790</v>
       </c>
     </row>
@@ -4924,11 +4922,11 @@
       <c r="T54">
         <v>2687</v>
       </c>
-      <c r="U54" s="1">
+      <c r="U54">
         <f t="shared" si="0"/>
         <v>26533</v>
       </c>
-      <c r="V54" s="1">
+      <c r="V54">
         <v>23529</v>
       </c>
     </row>
@@ -4993,11 +4991,11 @@
       <c r="T55">
         <v>3196</v>
       </c>
-      <c r="U55" s="1">
+      <c r="U55">
         <f t="shared" si="0"/>
         <v>29912</v>
       </c>
-      <c r="V55" s="1">
+      <c r="V55">
         <v>26438</v>
       </c>
     </row>
@@ -5062,11 +5060,11 @@
       <c r="T56">
         <v>3930</v>
       </c>
-      <c r="U56" s="1">
+      <c r="U56">
         <f t="shared" si="0"/>
         <v>37171</v>
       </c>
-      <c r="V56" s="1">
+      <c r="V56">
         <v>32815</v>
       </c>
     </row>
@@ -5131,11 +5129,11 @@
       <c r="T57">
         <v>5069</v>
       </c>
-      <c r="U57" s="1">
+      <c r="U57">
         <f t="shared" si="0"/>
         <v>46826</v>
       </c>
-      <c r="V57" s="1">
+      <c r="V57">
         <v>41390</v>
       </c>
     </row>
@@ -5200,11 +5198,11 @@
       <c r="T58">
         <v>7715</v>
       </c>
-      <c r="U58" s="1">
+      <c r="U58">
         <f t="shared" si="0"/>
         <v>68030</v>
       </c>
-      <c r="V58" s="1">
+      <c r="V58">
         <v>59783</v>
       </c>
     </row>
@@ -5269,11 +5267,11 @@
       <c r="T59">
         <v>19250</v>
       </c>
-      <c r="U59" s="1">
+      <c r="U59">
         <f t="shared" si="0"/>
         <v>168101</v>
       </c>
-      <c r="V59" s="1">
+      <c r="V59">
         <v>147633</v>
       </c>
     </row>
@@ -5338,11 +5336,11 @@
       <c r="T60">
         <v>21451</v>
       </c>
-      <c r="U60" s="1">
+      <c r="U60">
         <f t="shared" si="0"/>
         <v>191034</v>
       </c>
-      <c r="V60" s="1">
+      <c r="V60">
         <v>166942</v>
       </c>
     </row>
@@ -5407,11 +5405,11 @@
       <c r="T61">
         <v>28312</v>
       </c>
-      <c r="U61" s="1">
+      <c r="U61">
         <f t="shared" si="0"/>
         <v>245361</v>
       </c>
-      <c r="V61" s="1">
+      <c r="V61">
         <v>214612</v>
       </c>
     </row>
@@ -5476,11 +5474,11 @@
       <c r="T62">
         <v>35015</v>
       </c>
-      <c r="U62" s="1">
+      <c r="U62">
         <f t="shared" si="0"/>
         <v>288271</v>
       </c>
-      <c r="V62" s="1">
+      <c r="V62">
         <v>253399</v>
       </c>
     </row>
@@ -5545,11 +5543,11 @@
       <c r="T63">
         <v>39824</v>
       </c>
-      <c r="U63" s="1">
+      <c r="U63">
         <f t="shared" si="0"/>
         <v>313211</v>
       </c>
-      <c r="V63" s="1">
+      <c r="V63">
         <v>272912</v>
       </c>
     </row>
@@ -5614,11 +5612,11 @@
       <c r="T64">
         <v>44772</v>
       </c>
-      <c r="U64" s="1">
+      <c r="U64">
         <f t="shared" si="0"/>
         <v>342706</v>
       </c>
-      <c r="V64" s="1">
+      <c r="V64">
         <v>297239</v>
       </c>
     </row>
@@ -5683,11 +5681,11 @@
       <c r="T65">
         <v>59574</v>
       </c>
-      <c r="U65" s="1">
+      <c r="U65">
         <f t="shared" si="0"/>
         <v>444838</v>
       </c>
-      <c r="V65" s="1">
+      <c r="V65">
         <v>382654</v>
       </c>
     </row>
@@ -5752,11 +5750,11 @@
       <c r="T66">
         <v>68319</v>
       </c>
-      <c r="U66" s="1">
+      <c r="U66">
         <f t="shared" si="0"/>
         <v>495787</v>
       </c>
-      <c r="V66" s="1">
+      <c r="V66">
         <v>422236</v>
       </c>
     </row>
@@ -5821,11 +5819,11 @@
       <c r="T67">
         <v>85621</v>
       </c>
-      <c r="U67" s="1">
+      <c r="U67">
         <f t="shared" ref="U67:U83" si="1">SUM(B67:T67)</f>
         <v>622269</v>
       </c>
-      <c r="V67" s="1">
+      <c r="V67">
         <v>527899</v>
       </c>
     </row>
@@ -5890,11 +5888,11 @@
       <c r="T68">
         <v>72615</v>
       </c>
-      <c r="U68" s="1">
+      <c r="U68">
         <f t="shared" si="1"/>
         <v>531729</v>
       </c>
-      <c r="V68" s="1">
+      <c r="V68">
         <v>460031</v>
       </c>
     </row>
@@ -5959,11 +5957,11 @@
       <c r="T69">
         <v>67554</v>
       </c>
-      <c r="U69" s="1">
+      <c r="U69">
         <f t="shared" si="1"/>
         <v>463792</v>
       </c>
-      <c r="V69" s="1">
+      <c r="V69">
         <v>403001</v>
       </c>
     </row>
@@ -6028,11 +6026,11 @@
       <c r="T70">
         <v>73157</v>
       </c>
-      <c r="U70" s="1">
+      <c r="U70">
         <f t="shared" si="1"/>
         <v>496297</v>
       </c>
-      <c r="V70" s="1">
+      <c r="V70">
         <v>432923</v>
       </c>
     </row>
@@ -6097,11 +6095,11 @@
       <c r="T71">
         <v>81851</v>
       </c>
-      <c r="U71" s="1">
+      <c r="U71">
         <f t="shared" si="1"/>
         <v>567615</v>
       </c>
-      <c r="V71" s="1">
+      <c r="V71">
         <v>494331</v>
       </c>
     </row>
@@ -6166,11 +6164,11 @@
       <c r="T72">
         <v>86337</v>
       </c>
-      <c r="U72" s="1">
+      <c r="U72">
         <f t="shared" si="1"/>
         <v>582819</v>
       </c>
-      <c r="V72" s="1">
+      <c r="V72">
         <v>504308</v>
       </c>
     </row>
@@ -6235,11 +6233,11 @@
       <c r="T73">
         <v>98436</v>
       </c>
-      <c r="U73" s="1">
+      <c r="U73">
         <f t="shared" si="1"/>
         <v>665058</v>
       </c>
-      <c r="V73" s="1">
+      <c r="V73">
         <v>569234</v>
       </c>
     </row>
@@ -6304,11 +6302,11 @@
       <c r="T74">
         <v>102455</v>
       </c>
-      <c r="U74" s="1">
+      <c r="U74">
         <f t="shared" si="1"/>
         <v>671648</v>
       </c>
-      <c r="V74" s="1">
+      <c r="V74">
         <v>568963</v>
       </c>
     </row>
@@ -6373,11 +6371,11 @@
       <c r="T75">
         <v>104951</v>
       </c>
-      <c r="U75" s="1">
+      <c r="U75">
         <f t="shared" si="1"/>
         <v>691587</v>
       </c>
-      <c r="V75" s="1">
+      <c r="V75">
         <v>580925</v>
       </c>
     </row>
@@ -6442,11 +6440,11 @@
       <c r="T76">
         <v>107307</v>
       </c>
-      <c r="U76" s="1">
+      <c r="U76">
         <f t="shared" si="1"/>
         <v>695165</v>
       </c>
-      <c r="V76" s="1">
+      <c r="V76">
         <v>583054</v>
       </c>
     </row>
@@ -6511,11 +6509,11 @@
       <c r="T77">
         <v>124293</v>
       </c>
-      <c r="U77" s="1">
+      <c r="U77">
         <f t="shared" si="1"/>
         <v>813230</v>
       </c>
-      <c r="V77" s="1">
+      <c r="V77">
         <v>659623</v>
       </c>
     </row>
@@ -6580,11 +6578,11 @@
       <c r="T78">
         <v>117398</v>
       </c>
-      <c r="U78" s="1">
+      <c r="U78">
         <f t="shared" si="1"/>
         <v>730614</v>
       </c>
-      <c r="V78" s="1">
+      <c r="V78">
         <v>601334</v>
       </c>
     </row>
@@ -6649,11 +6647,11 @@
       <c r="T79">
         <v>111140</v>
       </c>
-      <c r="U79" s="1">
+      <c r="U79">
         <f t="shared" si="1"/>
         <v>715133</v>
       </c>
-      <c r="V79" s="1">
+      <c r="V79">
         <v>583765</v>
       </c>
     </row>
@@ -6718,11 +6716,11 @@
       <c r="T80">
         <v>106675</v>
       </c>
-      <c r="U80" s="1">
+      <c r="U80">
         <f t="shared" si="1"/>
         <v>658581</v>
       </c>
-      <c r="V80" s="1">
+      <c r="V80">
         <v>540346</v>
       </c>
     </row>
@@ -6787,11 +6785,11 @@
       <c r="T81">
         <v>81799</v>
       </c>
-      <c r="U81" s="1">
+      <c r="U81">
         <f t="shared" si="1"/>
         <v>495668</v>
       </c>
-      <c r="V81" s="1">
+      <c r="V81">
         <v>403338</v>
       </c>
     </row>
@@ -6856,11 +6854,11 @@
       <c r="T82">
         <v>82816</v>
       </c>
-      <c r="U82" s="1">
+      <c r="U82">
         <f t="shared" si="1"/>
         <v>495598</v>
       </c>
-      <c r="V82" s="1">
+      <c r="V82">
         <v>385431</v>
       </c>
     </row>
@@ -6925,11 +6923,11 @@
       <c r="T83">
         <v>39620</v>
       </c>
-      <c r="U83" s="1">
+      <c r="U83">
         <f t="shared" si="1"/>
         <v>228569</v>
       </c>
-      <c r="V83" s="1">
+      <c r="V83">
         <v>172928</v>
       </c>
     </row>
